--- a/Reporte_gastos/tabla_gastos_zonas_2026-3.xlsx
+++ b/Reporte_gastos/tabla_gastos_zonas_2026-3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t xml:space="preserve">TIENDA</t>
   </si>
@@ -21,6 +21,15 @@
   </si>
   <si>
     <t xml:space="preserve">Sueldos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incentivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contribuciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total_sueldos</t>
   </si>
   <si>
     <t xml:space="preserve">Alquileres</t>
@@ -425,326 +434,461 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="n">
         <v>63788150.53</v>
       </c>
       <c r="C2" t="n">
+        <v>3527927.24744444</v>
+      </c>
+      <c r="D2" t="n">
+        <v>205190</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1145262.79689529</v>
+      </c>
+      <c r="F2" t="n">
         <v>4878380.04433974</v>
       </c>
-      <c r="D2" t="n">
+      <c r="G2" t="n">
         <v>7100000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>482850.5</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>7582850.5</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>2290137.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="n">
         <v>29608257.6</v>
       </c>
       <c r="C3" t="n">
+        <v>2345881.77</v>
+      </c>
+      <c r="D3" t="n">
+        <v>114281</v>
+      </c>
+      <c r="E3" t="n">
+        <v>746636.994165</v>
+      </c>
+      <c r="F3" t="n">
         <v>3206799.764165</v>
       </c>
-      <c r="D3" t="n">
+      <c r="G3" t="n">
         <v>2300000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="H3" t="n">
         <v>2262542.07</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>4562542.07</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>417466.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="n">
         <v>93396408.13</v>
       </c>
       <c r="C4" t="n">
+        <v>5873809.01744444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>319471</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1891899.79106029</v>
+      </c>
+      <c r="F4" t="n">
         <v>8085179.80850474</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
         <v>9400000</v>
       </c>
-      <c r="E4" t="n">
+      <c r="H4" t="n">
         <v>2745392.57</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>12145392.57</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>2707603.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="n">
         <v>33874570.08</v>
       </c>
       <c r="C5" t="n">
+        <v>2337980.12781644</v>
+      </c>
+      <c r="D5" t="n">
+        <v>138656</v>
+      </c>
+      <c r="E5" t="n">
+        <v>752155.910494251</v>
+      </c>
+      <c r="F5" t="n">
         <v>3228792.03831069</v>
       </c>
-      <c r="D5" t="n">
+      <c r="G5" t="n">
         <v>2012472</v>
       </c>
-      <c r="E5" t="n">
+      <c r="H5" t="n">
         <v>599981.67</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>2612453.67</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>352366.35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B6" t="n">
         <v>22059683.74</v>
       </c>
       <c r="C6" t="n">
+        <v>2212554.90575472</v>
+      </c>
+      <c r="D6" t="n">
+        <v>96183</v>
+      </c>
+      <c r="E6" t="n">
+        <v>707962.4722225</v>
+      </c>
+      <c r="F6" t="n">
         <v>3016700.37797722</v>
       </c>
-      <c r="D6" t="n">
+      <c r="G6" t="n">
         <v>923100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="H6" t="n">
         <v>319028.67</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>1242128.67</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>537100.82</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B7" t="n">
         <v>55934253.82</v>
       </c>
       <c r="C7" t="n">
+        <v>4550535.03357116</v>
+      </c>
+      <c r="D7" t="n">
+        <v>234839</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1460118.38271675</v>
+      </c>
+      <c r="F7" t="n">
         <v>6245492.41628791</v>
       </c>
-      <c r="D7" t="n">
+      <c r="G7" t="n">
         <v>2935572</v>
       </c>
-      <c r="E7" t="n">
+      <c r="H7" t="n">
         <v>919010.34</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>3854582.34</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>889467.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>3804986.83</v>
       </c>
       <c r="C8" t="n">
+        <v>1326168.58464646</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12812</v>
+      </c>
+      <c r="E8" t="n">
+        <v>409576.672263391</v>
+      </c>
+      <c r="F8" t="n">
         <v>1748557.25690986</v>
       </c>
-      <c r="D8" t="n">
+      <c r="G8" t="n">
         <v>715965.54</v>
       </c>
-      <c r="E8" t="n">
+      <c r="H8" t="n">
         <v>373918.78</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>1089884.32</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>358712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" t="n">
         <v>15136894.1</v>
       </c>
       <c r="C9" t="n">
+        <v>2084243.82642884</v>
+      </c>
+      <c r="D9" t="n">
+        <v>35802</v>
+      </c>
+      <c r="E9" t="n">
+        <v>649636.354823249</v>
+      </c>
+      <c r="F9" t="n">
         <v>2769682.18125209</v>
       </c>
-      <c r="D9" t="n">
+      <c r="G9" t="n">
         <v>1070367.2</v>
       </c>
-      <c r="E9" t="n">
+      <c r="H9" t="n">
         <v>599981.67</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>1670348.87</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>368667.34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
         <v>18941880.93</v>
       </c>
       <c r="C10" t="n">
+        <v>3410412.41107531</v>
+      </c>
+      <c r="D10" t="n">
+        <v>48614</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1059213.02708664</v>
+      </c>
+      <c r="F10" t="n">
         <v>4518239.43816195</v>
       </c>
-      <c r="D10" t="n">
+      <c r="G10" t="n">
         <v>1786332.74</v>
       </c>
-      <c r="E10" t="n">
+      <c r="H10" t="n">
         <v>973900.45</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>2760233.19</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>727379.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" t="n">
         <v>8695899.86</v>
       </c>
       <c r="C11" t="n">
+        <v>1342184.75805216</v>
+      </c>
+      <c r="D11" t="n">
+        <v>34876</v>
+      </c>
+      <c r="E11" t="n">
+        <v>420545.603689261</v>
+      </c>
+      <c r="F11" t="n">
         <v>1797606.36174142</v>
       </c>
-      <c r="D11" t="n">
+      <c r="G11" t="n">
         <v>583226.46</v>
       </c>
-      <c r="E11" t="n">
+      <c r="H11" t="n">
         <v>57207.09</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>640433.55</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>46108.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>10327999.73</v>
       </c>
       <c r="C12" t="n">
+        <v>2793428.17985693</v>
+      </c>
+      <c r="D12" t="n">
+        <v>57249</v>
+      </c>
+      <c r="E12" t="n">
+        <v>872969.797592057</v>
+      </c>
+      <c r="F12" t="n">
         <v>3723646.97744899</v>
       </c>
-      <c r="D12" t="n">
+      <c r="G12" t="n">
         <v>1872828.43</v>
       </c>
-      <c r="E12" t="n">
+      <c r="H12" t="n">
         <v>173089.62</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>2045918.05</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>43291.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" t="n">
         <v>19023899.59</v>
       </c>
       <c r="C13" t="n">
+        <v>4135612.93790909</v>
+      </c>
+      <c r="D13" t="n">
+        <v>92125</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1293515.40128132</v>
+      </c>
+      <c r="F13" t="n">
         <v>5521253.33919041</v>
       </c>
-      <c r="D13" t="n">
+      <c r="G13" t="n">
         <v>2456054.89</v>
       </c>
-      <c r="E13" t="n">
+      <c r="H13" t="n">
         <v>230296.71</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>2686351.6</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>89400.06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
         <v>14652695.72</v>
       </c>
       <c r="C14" t="n">
+        <v>2331595.72</v>
+      </c>
+      <c r="D14" t="n">
+        <v>43692</v>
+      </c>
+      <c r="E14" t="n">
+        <v>724214.127465</v>
+      </c>
+      <c r="F14" t="n">
         <v>3099501.847465</v>
       </c>
-      <c r="D14" t="n">
+      <c r="G14" t="n">
         <v>1026394.29</v>
       </c>
-      <c r="E14" t="n">
+      <c r="H14" t="n">
         <v>1199963.34</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>2226357.63</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>485004.42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" t="n">
         <v>201949138.19</v>
       </c>
       <c r="C15" t="n">
+        <v>20301965.12</v>
+      </c>
+      <c r="D15" t="n">
+        <v>738741</v>
+      </c>
+      <c r="E15" t="n">
+        <v>6428960.72961</v>
+      </c>
+      <c r="F15" t="n">
         <v>27469666.84961</v>
       </c>
-      <c r="D15" t="n">
+      <c r="G15" t="n">
         <v>17604353.92</v>
       </c>
-      <c r="E15" t="n">
+      <c r="H15" t="n">
         <v>6068563.41</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>23672917.33</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>4898854.42</v>
       </c>
     </row>
